--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2020/WYOMING_2020.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2020/WYOMING_2020.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D246"/>
+  <dimension ref="A1:D240"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Asientos</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pabellón de Arteaga</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C5">
@@ -434,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C6">
@@ -447,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -491,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -542,7 +582,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C13">
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Arriaga</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Bachíniva</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Bocoyna</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Camargo</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -688,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Gran Morelos</t>
@@ -701,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Guerero</t>
@@ -714,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C26">
@@ -727,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Ignacio Zaragoza</t>
@@ -740,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -753,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -766,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Meoqui</t>
@@ -779,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Namiquipa</t>
@@ -792,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -805,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Ojinaga</t>
@@ -818,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Praxedis G. Guerero</t>
@@ -831,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Rosario</t>
@@ -844,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Santa Isabel</t>
@@ -857,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -888,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Monclova</t>
@@ -901,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Progreso</t>
@@ -914,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -927,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Viesca</t>
@@ -940,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Total</t>
@@ -971,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Colima</t>
@@ -984,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -997,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Tecomán</t>
@@ -1010,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1025,7 +1225,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1041,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1054,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1067,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cuajimalpa de Morelos</t>
+          <t>Cuajimalpa De Morelos</t>
         </is>
       </c>
       <c r="C52">
@@ -1080,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1093,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1106,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1119,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1132,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>La Magdalena Contreras</t>
@@ -1145,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1158,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1171,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1191,7 +1446,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Coneto de Comonfort</t>
+          <t>Coneto De Comonfort</t>
         </is>
       </c>
       <c r="C61">
@@ -1202,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -1215,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -1228,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Nazas</t>
@@ -1241,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nombre de Dios</t>
+          <t>Nombre De Dios</t>
         </is>
       </c>
       <c r="C65">
@@ -1254,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>San Bernardo</t>
@@ -1267,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Vicente Guerero</t>
@@ -1280,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1295,12 +1585,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Coacalco de Berriozábal</t>
+          <t>Coacalco De Berriozábal</t>
         </is>
       </c>
       <c r="C69">
@@ -1311,9 +1601,14 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C70">
@@ -1324,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -1337,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1350,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C73">
@@ -1363,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C74">
@@ -1376,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1389,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1404,7 +1729,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1420,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Cuerámaro</t>
@@ -1433,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Doctor Mora</t>
@@ -1446,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C80">
@@ -1459,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1472,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>León</t>
@@ -1485,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -1498,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -1511,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -1524,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Santa Cruz de Juventino Rosas</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C86">
@@ -1537,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Tarandacuao</t>
@@ -1550,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -1588,7 +1968,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C90">
@@ -1599,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>General Heliodoro Castillo</t>
@@ -1612,9 +1997,14 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C92">
@@ -1625,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -1638,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1669,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Francisco I. Madero</t>
@@ -1682,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Huehuetla</t>
@@ -1695,9 +2105,14 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Huejutla de Reyes</t>
+          <t>Huejutla De Reyes</t>
         </is>
       </c>
       <c r="C98">
@@ -1708,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -1721,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -1734,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C101">
@@ -1747,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Pacula</t>
@@ -1760,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Progreso de Obregón</t>
+          <t>Progreso De Obregón</t>
         </is>
       </c>
       <c r="C103">
@@ -1773,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1804,9 +2249,14 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C106">
@@ -1817,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -1830,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Casimiro Castillo</t>
@@ -1843,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -1856,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Colotlán</t>
@@ -1869,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -1882,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -1895,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1908,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Jalostotitlán</t>
@@ -1921,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Juchitlán</t>
@@ -1934,9 +2429,14 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C116">
@@ -1947,9 +2447,14 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>San Juan de los Lagos</t>
+          <t>San Juan De Los Lagos</t>
         </is>
       </c>
       <c r="C117">
@@ -1960,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>San Julián</t>
@@ -1973,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -1986,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C120">
@@ -1999,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Tapalpa</t>
@@ -2012,9 +2537,14 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C122">
@@ -2025,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -2038,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Tomatlán</t>
@@ -2051,9 +2591,14 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C125">
@@ -2064,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -2077,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2108,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Ixtlán</t>
@@ -2121,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -2134,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -2147,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -2160,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Queréndaro</t>
@@ -2173,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Santa Ana Maya</t>
@@ -2186,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Tancítaro</t>
@@ -2199,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -2212,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -2225,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -2238,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -2251,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2271,7 +2886,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Puente de Ixtla</t>
+          <t>Puente De Ixtla</t>
         </is>
       </c>
       <c r="C141">
@@ -2282,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2313,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Compostela</t>
@@ -2326,9 +2951,14 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Santa María del Oro</t>
+          <t>Santa María Del Oro</t>
         </is>
       </c>
       <c r="C145">
@@ -2339,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -2352,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2383,9 +3023,14 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C149">
@@ -2396,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2416,7 +3066,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Ejutla de Crespo</t>
+          <t>Heroica Ciudad De Ejutla De Crespo</t>
         </is>
       </c>
       <c r="C151">
@@ -2427,9 +3077,14 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Pinotepa de Don Luis</t>
+          <t>Pinotepa De Don Luis</t>
         </is>
       </c>
       <c r="C152">
@@ -2440,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>San Juan Bautista Atatlahuca</t>
@@ -2453,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>San Juan Lachao</t>
@@ -2466,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>San Juan Lalana</t>
@@ -2479,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>San Martín Peras</t>
@@ -2492,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Santos Reyes Nopala</t>
@@ -2505,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2536,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Cuautempan</t>
@@ -2549,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Esperanza</t>
@@ -2562,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -2575,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Jopala</t>
@@ -2588,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Naupan</t>
@@ -2601,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -2614,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>San Pablo Anicano</t>
@@ -2627,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -2640,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -2653,9 +3383,14 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Tepexi de Rodríguez</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C169">
@@ -2666,9 +3401,14 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C170">
@@ -2679,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Tlapacoya</t>
@@ -2692,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Vicente Guerero</t>
@@ -2705,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Yehualtepec</t>
@@ -2718,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2738,7 +3498,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C175">
@@ -2749,9 +3509,14 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C176">
@@ -2762,9 +3527,14 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C177">
@@ -2775,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2806,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -2819,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -2832,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>San Martín Chalchicuautla</t>
@@ -2845,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Santa María del Río</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C183">
@@ -2858,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Santo Domingo</t>
@@ -2871,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2902,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Badiraguato</t>
@@ -2915,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Choix</t>
@@ -2928,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -2941,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -2954,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Mocorito</t>
@@ -2967,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2998,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Cajeme</t>
@@ -3011,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Guaymas</t>
@@ -3024,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -3037,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Sahuaripa</t>
@@ -3050,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3081,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Jalapa</t>
@@ -3094,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3125,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -3138,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Xicoténcatl</t>
@@ -3151,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3171,7 +4056,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Acuamanala de Miguel Hidalgo</t>
+          <t>Acuamanala De Miguel Hidalgo</t>
         </is>
       </c>
       <c r="C206">
@@ -3182,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Apizaco</t>
@@ -3195,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Calpulalpan</t>
@@ -3208,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -3221,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Cuaxomulco</t>
@@ -3234,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Hueyotlipan</t>
@@ -3247,9 +4157,14 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Muñoz de Domingo Arenas</t>
+          <t>Muñoz De Domingo Arenas</t>
         </is>
       </c>
       <c r="C212">
@@ -3260,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Santa Cruz Tlaxcala</t>
@@ -3273,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -3286,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -3299,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Xaloztoc</t>
@@ -3312,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Xaltocan</t>
@@ -3325,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3356,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -3369,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -3382,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Tihuatlán</t>
@@ -3395,6 +4355,11 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Tlaquilpa</t>
@@ -3408,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3439,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3470,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -3483,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Genaro Codina</t>
@@ -3496,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>General Francisco R. Murguía</t>
@@ -3509,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -3522,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Monte Escobedo</t>
@@ -3535,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -3548,9 +4553,14 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C234">
@@ -3561,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -3574,9 +4589,14 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C236">
@@ -3587,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Villa González Ortega</t>
@@ -3600,6 +4625,11 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -3613,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3636,41 +4671,6 @@
       </c>
       <c r="D240">
         <v>1</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 497,795</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Octubre de 2021</t>
-        </is>
       </c>
     </row>
   </sheetData>
